--- a/我的工作脈絡/專案階段表.xlsx
+++ b/我的工作脈絡/專案階段表.xlsx
@@ -793,7 +793,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>・「這階段會收到什麼信」＋「來自誰」＋「大約時間」三欄合起來，就是小幫手的「該來沒來」提醒：時間到了還沒收到，報告會提醒你。</t>
+          <t>・「這階段會收到什麼信」＋「來自誰」＋「大約時間」三欄合起來，就是小幫手的「例行交件提醒」：每期固定要收、有期限的東西（例如每學期名單、每月報表），過了期限還沒收到，報告會提醒你。</t>
         </is>
       </c>
     </row>
